--- a/Diplomarbeiten.xlsx
+++ b/Diplomarbeiten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://htlvbat-my.sharepoint.com/personal/m_schachinger_htlvb_at/Documents/5AHWII/SWP/FriendOfAwardBewertung1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://htlvbat-my.sharepoint.com/personal/l_seiringer_htlvb_at/Documents/SWP/5/FriendOfBewertungV2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB5A7171-A33A-45B0-876F-C862E3ADB09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0139DE6D-208B-4417-A438-7025953F45FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{54849071-C0FB-4584-8F80-E1E677421741}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D126F0-A4AF-41E2-A521-955887EB6AB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,18 +36,138 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>Nerf-Gun</t>
-  </si>
-  <si>
-    <t>Website</t>
-  </si>
-  <si>
-    <t>Roboter</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <si>
+    <t>Laufende Nummer</t>
+  </si>
+  <si>
+    <t>Titel der Diplomarbeit</t>
+  </si>
+  <si>
+    <t>Name(n) der Schüler:innen</t>
+  </si>
+  <si>
+    <t>Punkte Schulvoting</t>
+  </si>
+  <si>
+    <t>Projekt Alpha</t>
+  </si>
+  <si>
+    <t>Max Mustermann, Lisa Beispiel</t>
+  </si>
+  <si>
+    <t>Projekt Beta</t>
+  </si>
+  <si>
+    <t>Anna Huber, Paul Maier</t>
+  </si>
+  <si>
+    <t>Projekt Gamma</t>
+  </si>
+  <si>
+    <t>Julia Steiner, Tom Berger</t>
+  </si>
+  <si>
+    <t>Projekt Delta</t>
+  </si>
+  <si>
+    <t>Simon Gruber, Nina Wolf</t>
+  </si>
+  <si>
+    <t>Projekt Epsilon</t>
+  </si>
+  <si>
+    <t>Markus Hofer, Lena Koch</t>
+  </si>
+  <si>
+    <t>Projekt Zeta</t>
+  </si>
+  <si>
+    <t>David Leitner, Sarah Bauer</t>
+  </si>
+  <si>
+    <t>Projekt Eta</t>
+  </si>
+  <si>
+    <t>Florian Schwarz, Eva Lang</t>
+  </si>
+  <si>
+    <t>Projekt Theta</t>
+  </si>
+  <si>
+    <t>Manuel Fuchs, Katharina Weiss</t>
+  </si>
+  <si>
+    <t>Projekt Iota</t>
+  </si>
+  <si>
+    <t>Lukas König, Laura Aigner</t>
+  </si>
+  <si>
+    <t>Projekt Kappa</t>
+  </si>
+  <si>
+    <t>Patrick Pichler, Sophie Moser</t>
+  </si>
+  <si>
+    <t>Projekt Lambda</t>
+  </si>
+  <si>
+    <t>Alexander Baumann, Miriam Haas</t>
+  </si>
+  <si>
+    <t>Projekt Mu</t>
+  </si>
+  <si>
+    <t>Benjamin Seidl, Verena Winkler</t>
+  </si>
+  <si>
+    <t>Projekt Nu</t>
+  </si>
+  <si>
+    <t>Michael Brandner, Daniela Ortner</t>
+  </si>
+  <si>
+    <t>Projekt Xi</t>
+  </si>
+  <si>
+    <t>Stefan Reiter, Carina Beck</t>
+  </si>
+  <si>
+    <t>Projekt Omikron</t>
+  </si>
+  <si>
+    <t>Andreas Leitgeb, Julia Höller</t>
+  </si>
+  <si>
+    <t>Projekt Pi</t>
+  </si>
+  <si>
+    <t>Christian Eder, Melanie Graf</t>
+  </si>
+  <si>
+    <t>Projekt Rho</t>
+  </si>
+  <si>
+    <t>Thomas Mayr, Sabine Leitner</t>
+  </si>
+  <si>
+    <t>Projekt Sigma</t>
+  </si>
+  <si>
+    <t>Dominik Kraus, Petra Schmid</t>
+  </si>
+  <si>
+    <t>Projekt Tau</t>
+  </si>
+  <si>
+    <t>Roman Huber, Claudia Neumann</t>
+  </si>
+  <si>
+    <t>Projekt Omega</t>
+  </si>
+  <si>
+    <t>Martin Brunner, Franziska Kurz</t>
   </si>
 </sst>
 </file>
@@ -418,43 +538,308 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E39F0D0-17F2-4CB7-8CF5-341190220B93}">
-  <dimension ref="A1:B4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77EF633A-C242-4C00-8DC8-C7981ED1E1C3}">
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Diplomarbeiten.xlsx
+++ b/Diplomarbeiten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://htlvbat-my.sharepoint.com/personal/l_seiringer_htlvb_at/Documents/SWP/5/FriendOfBewertungV2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://htlvbat-my.sharepoint.com/personal/m_schachinger_htlvb_at/Documents/5AHWII/SWP/FriendOfAwardBewertung1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0139DE6D-208B-4417-A438-7025953F45FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{0139DE6D-208B-4417-A438-7025953F45FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63E3378-2DAE-4FD9-BBCF-AEAECE039F2F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D126F0-A4AF-41E2-A521-955887EB6AB0}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{A9D126F0-A4AF-41E2-A521-955887EB6AB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,6 @@
     <t>Punkte Schulvoting</t>
   </si>
   <si>
-    <t>Projekt Alpha</t>
-  </si>
-  <si>
     <t>Max Mustermann, Lisa Beispiel</t>
   </si>
   <si>
@@ -168,6 +165,9 @@
   </si>
   <si>
     <t>Martin Brunner, Franziska Kurz</t>
+  </si>
+  <si>
+    <t>Projekt tscheire</t>
   </si>
 </sst>
 </file>
@@ -567,13 +567,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
       <c r="D2">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -581,10 +581,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
       <c r="D3">
         <v>35</v>
@@ -595,10 +595,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
       </c>
       <c r="D4">
         <v>34</v>
@@ -609,10 +609,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="D5">
         <v>33</v>
@@ -623,10 +623,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
       </c>
       <c r="D6">
         <v>32</v>
@@ -637,10 +637,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
       </c>
       <c r="D7">
         <v>31</v>
@@ -651,10 +651,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
       </c>
       <c r="D8">
         <v>30</v>
@@ -665,10 +665,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
       </c>
       <c r="D9">
         <v>29</v>
@@ -679,10 +679,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
       </c>
       <c r="D10">
         <v>28</v>
@@ -693,10 +693,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
       </c>
       <c r="D11">
         <v>27</v>
@@ -707,10 +707,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
       </c>
       <c r="D12">
         <v>26</v>
@@ -721,10 +721,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
       </c>
       <c r="D13">
         <v>25</v>
@@ -735,10 +735,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
         <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
       </c>
       <c r="D14">
         <v>24</v>
@@ -749,10 +749,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
       </c>
       <c r="D15">
         <v>23</v>
@@ -763,10 +763,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
         <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
       </c>
       <c r="D16">
         <v>22</v>
@@ -777,10 +777,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
         <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
       </c>
       <c r="D17">
         <v>21</v>
@@ -791,10 +791,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
         <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
       </c>
       <c r="D18">
         <v>20</v>
@@ -805,10 +805,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
         <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
       </c>
       <c r="D19">
         <v>19</v>
@@ -819,10 +819,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
         <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
       </c>
       <c r="D20">
         <v>18</v>
@@ -833,10 +833,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
         <v>42</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
       </c>
       <c r="D21">
         <v>17</v>
